--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -831,6 +832,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1004,6 +1006,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
@@ -8501,24 +8504,48 @@
       </c>
       <c r="B25" s="37" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="90" t="n"/>
-      <c r="E25" s="90" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="90" t="n">
+        <v>46279.01908564815</v>
+      </c>
+      <c r="E25" s="90" t="n">
+        <v>46279.88167824074</v>
+      </c>
       <c r="F25" s="85">
         <f>IF(OR(D25="",E25=""),"",24*(E25-D25))</f>
         <v/>
       </c>
-      <c r="G25" s="86" t="n"/>
-      <c r="H25" s="86" t="n"/>
-      <c r="I25" s="86" t="n"/>
-      <c r="J25" s="86" t="n"/>
-      <c r="K25" s="86" t="n"/>
-      <c r="L25" s="86" t="n"/>
-      <c r="M25" s="86" t="n"/>
-      <c r="N25" s="86" t="n"/>
+      <c r="G25" s="86" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H25" s="86" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I25" s="86" t="n">
+        <v>1654</v>
+      </c>
+      <c r="J25" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="86" t="n">
+        <v>91</v>
+      </c>
+      <c r="L25" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="M25" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="86" t="n">
+        <v>15208</v>
+      </c>
       <c r="O25" s="86" t="n">
         <v>5</v>
       </c>
@@ -8527,7 +8554,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q25" s="37" t="n"/>
+      <c r="Q25" s="37" t="inlineStr">
+        <is>
+          <t>Run ID 24; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="76" t="n">
@@ -16872,6 +16903,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -17165,6 +17197,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -832,7 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1006,7 +1005,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
@@ -8566,24 +8564,48 @@
       </c>
       <c r="B26" s="36" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="89" t="n"/>
-      <c r="E26" s="89" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" s="89" t="n">
+        <v>46280.02366898148</v>
+      </c>
+      <c r="E26" s="89" t="n">
+        <v>46280.91341435185</v>
+      </c>
       <c r="F26" s="82">
         <f>IF(OR(D26="",E26=""),"",24*(E26-D26))</f>
         <v/>
       </c>
-      <c r="G26" s="83" t="n"/>
-      <c r="H26" s="83" t="n"/>
-      <c r="I26" s="83" t="n"/>
-      <c r="J26" s="83" t="n"/>
-      <c r="K26" s="83" t="n"/>
-      <c r="L26" s="83" t="n"/>
-      <c r="M26" s="83" t="n"/>
-      <c r="N26" s="83" t="n"/>
+      <c r="G26" s="83" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H26" s="83" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I26" s="83" t="n">
+        <v>1572</v>
+      </c>
+      <c r="J26" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="83" t="n">
+        <v>168</v>
+      </c>
+      <c r="L26" s="83" t="n">
+        <v>20</v>
+      </c>
+      <c r="M26" s="83" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="83" t="n">
+        <v>14392</v>
+      </c>
       <c r="O26" s="83" t="n">
         <v>5</v>
       </c>
@@ -8592,7 +8614,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q26" s="36" t="n"/>
+      <c r="Q26" s="36" t="inlineStr">
+        <is>
+          <t>Run ID 25; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="79" t="n">
@@ -8600,11 +8626,17 @@
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C27" s="37" t="n"/>
-      <c r="D27" s="90" t="n"/>
+          <t>Đang chạy</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D27" s="90" t="n">
+        <v>46281.02569444444</v>
+      </c>
       <c r="E27" s="90" t="n"/>
       <c r="F27" s="85">
         <f>IF(OR(D27="",E27=""),"",24*(E27-D27))</f>
@@ -8626,7 +8658,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q27" s="37" t="n"/>
+      <c r="Q27" s="37" t="inlineStr">
+        <is>
+          <t>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="76" t="n">
@@ -16903,7 +16939,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -17197,7 +17232,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -832,6 +832,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -1005,6 +1006,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
@@ -8626,7 +8628,7 @@
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>Đang chạy</t>
+          <t>Hoàn thành có lỗi</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
@@ -8635,21 +8637,39 @@
         </is>
       </c>
       <c r="D27" s="90" t="n">
-        <v>46281.02569444444</v>
-      </c>
-      <c r="E27" s="90" t="n"/>
+        <v>46281.02523148148</v>
+      </c>
+      <c r="E27" s="90" t="n">
+        <v>46281.85599537037</v>
+      </c>
       <c r="F27" s="85">
         <f>IF(OR(D27="",E27=""),"",24*(E27-D27))</f>
         <v/>
       </c>
-      <c r="G27" s="86" t="n"/>
-      <c r="H27" s="86" t="n"/>
-      <c r="I27" s="86" t="n"/>
-      <c r="J27" s="86" t="n"/>
-      <c r="K27" s="86" t="n"/>
-      <c r="L27" s="86" t="n"/>
-      <c r="M27" s="86" t="n"/>
-      <c r="N27" s="86" t="n"/>
+      <c r="G27" s="86" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H27" s="86" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I27" s="86" t="n">
+        <v>1559</v>
+      </c>
+      <c r="J27" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="86" t="n">
+        <v>181</v>
+      </c>
+      <c r="L27" s="86" t="n">
+        <v>20</v>
+      </c>
+      <c r="M27" s="86" t="n">
+        <v>10</v>
+      </c>
+      <c r="N27" s="86" t="n">
+        <v>13640</v>
+      </c>
       <c r="O27" s="86" t="n">
         <v>5</v>
       </c>
@@ -8660,7 +8680,7 @@
       </c>
       <c r="Q27" s="37" t="inlineStr">
         <is>
-          <t>Scheduled VPS crawl đã tạo trên deploy; artifact không lưu</t>
+          <t>Run ID 26; deploy https://hotel.projecthub.io.vn/; artifact không lưu; scraper_version 2.3.0; terminal API status completed; items pagination 1770; saved_options_count 13640.</t>
         </is>
       </c>
     </row>
@@ -16939,6 +16959,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -17232,6 +17253,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -311,6 +311,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -320,15 +332,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -816,21 +819,22 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="26" customWidth="1" style="36" min="1" max="1"/>
-    <col width="22" customWidth="1" style="36" min="2" max="2"/>
-    <col width="4" customWidth="1" style="36" min="3" max="3"/>
-    <col width="28" customWidth="1" style="36" min="4" max="4"/>
-    <col width="18" customWidth="1" style="36" min="5" max="5"/>
+    <col width="26" customWidth="1" style="40" min="1" max="1"/>
+    <col width="22" customWidth="1" style="40" min="2" max="2"/>
+    <col width="4" customWidth="1" style="40" min="3" max="3"/>
+    <col width="28" customWidth="1" style="40" min="4" max="4"/>
+    <col width="18" customWidth="1" style="40" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>LỊCH CRAWL VPS BỔ SUNG — 24/08/2026 ĐẾN 30/11/2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Thông số</t>
@@ -1003,8 +1007,9 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>VPS theo dõi 5 anchor bổ sung có chủ đích. Mỗi ngày được đối chiếu trực tiếp với 12 ngày local; không chọn ngẫu nhiên lại và không dùng slot trùng local.</t>
         </is>
@@ -1034,30 +1039,30 @@
   <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="14" customWidth="1" style="36" min="1" max="1"/>
-    <col width="13" customWidth="1" style="36" min="2" max="2"/>
-    <col width="12" customWidth="1" style="36" min="3" max="3"/>
-    <col width="15" customWidth="1" style="36" min="4" max="9"/>
-    <col width="10" customWidth="1" style="36" min="10" max="11"/>
-    <col width="18" customWidth="1" style="36" min="12" max="14"/>
-    <col width="22" customWidth="1" style="36" min="15" max="15"/>
+    <col width="14" customWidth="1" style="40" min="1" max="1"/>
+    <col width="13" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="15" customWidth="1" style="40" min="4" max="9"/>
+    <col width="10" customWidth="1" style="40" min="10" max="11"/>
+    <col width="18" customWidth="1" style="40" min="12" max="14"/>
+    <col width="22" customWidth="1" style="40" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>VPS CRAWL PLAN — 99 NGÀY, 5 CHECK-IN BỔ SUNG MỖI NGÀY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>V1–V5 là anchor bổ sung. Tất cả check-in phải &gt;= crawl date, khác nhau và không xuất hiện trong 12 slot local của cùng ngày crawl.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Crawl date</t>
@@ -7100,30 +7105,30 @@
   <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="14" customWidth="1" style="36" min="1" max="1"/>
-    <col width="20" customWidth="1" style="36" min="2" max="2"/>
-    <col width="12" customWidth="1" style="36" min="3" max="3"/>
-    <col width="19" customWidth="1" style="42" min="4" max="5"/>
-    <col width="16" customWidth="1" style="36" min="6" max="6"/>
-    <col width="13" customWidth="1" style="36" min="7" max="16"/>
-    <col width="38" customWidth="1" style="36" min="17" max="17"/>
+    <col width="14" customWidth="1" style="40" min="1" max="1"/>
+    <col width="20" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="19" customWidth="1" style="43" min="4" max="5"/>
+    <col width="16" customWidth="1" style="40" min="6" max="6"/>
+    <col width="13" customWidth="1" style="40" min="7" max="16"/>
+    <col width="38" customWidth="1" style="40" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>VPS CRAWL LOG — MỖI NGÀY MỘT DÒNG</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Ghi một dòng cho mỗi crawl date. Từ 03/09/2026, VPS dùng 354 khách sạn × 5 check-in = 1.770 item dự kiến; các run cũ giữ số item thực tế; không lưu HTML nếu không cần kiểm tra.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Crawl date</t>
@@ -7222,10 +7227,10 @@
       <c r="C4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="35" t="n">
         <v>46258.02627314815</v>
       </c>
-      <c r="E4" s="39" t="n">
+      <c r="E4" s="35" t="n">
         <v>46258.71729166667</v>
       </c>
       <c r="F4" s="19">
@@ -7279,10 +7284,10 @@
         <f>C4+1</f>
         <v/>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="36" t="n">
         <v>46259.03542824074</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="36" t="n">
         <v>46259.75431712963</v>
       </c>
       <c r="F5" s="20">
@@ -7335,10 +7340,10 @@
       <c r="C6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="35" t="n">
         <v>46260.0284375</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="35" t="n">
         <v>46260.77434027778</v>
       </c>
       <c r="F6" s="19" t="n">
@@ -7390,10 +7395,10 @@
       <c r="C7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="36" t="n">
         <v>46261.02307870371</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="36" t="n">
         <v>46261.93287037037</v>
       </c>
       <c r="F7" s="20" t="n">
@@ -7449,10 +7454,10 @@
       <c r="C8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="35" t="n">
         <v>46262.03721064814</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="35" t="n">
         <v>46262.85714120371</v>
       </c>
       <c r="F8" s="19" t="n">
@@ -7504,10 +7509,10 @@
       <c r="C9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="36" t="n">
         <v>46262.73239583334</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="36" t="n">
         <v>46263.90916666666</v>
       </c>
       <c r="F9" s="20" t="n">
@@ -7563,10 +7568,10 @@
       <c r="C10" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="35" t="n">
         <v>46263.73232638889</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="35" t="n">
         <v>46264.50788194445</v>
       </c>
       <c r="F10" s="19" t="n">
@@ -7618,10 +7623,10 @@
       <c r="C11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="36" t="n">
         <v>46264.73168981481</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="36" t="n">
         <v>46265.57034722222</v>
       </c>
       <c r="F11" s="20" t="n">
@@ -7677,10 +7682,10 @@
       <c r="C12" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="35" t="n">
         <v>46265.73229166667</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="35" t="n">
         <v>46266.5821412037</v>
       </c>
       <c r="F12" s="19" t="n">
@@ -7736,10 +7741,10 @@
       <c r="C13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="36" t="n">
         <v>46267.02332175926</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="36" t="n">
         <v>46267.89032407408</v>
       </c>
       <c r="F13" s="20" t="n">
@@ -7795,10 +7800,10 @@
       <c r="C14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="35" t="n">
         <v>46268.02444444445</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="35" t="n">
         <v>46268.80280092593</v>
       </c>
       <c r="F14" s="19" t="n">
@@ -7854,10 +7859,10 @@
       <c r="C15" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="36" t="n">
         <v>46269.02368055555</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="36" t="n">
         <v>46269.90994212963</v>
       </c>
       <c r="F15" s="20" t="n">
@@ -7913,10 +7918,10 @@
       <c r="C16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="37" t="n">
         <v>46151.02291666667</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="35" t="n">
         <v>46270.93908564815</v>
       </c>
       <c r="F16" s="19" t="n">
@@ -7968,10 +7973,10 @@
       <c r="C17" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="36" t="n">
         <v>46271.02481481482</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="36" t="n">
         <v>46271.98013888889</v>
       </c>
       <c r="F17" s="20" t="n">
@@ -8023,10 +8028,10 @@
       <c r="C18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="35" t="n">
         <v>46272.02271990741</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="35" t="n">
         <v>46272.93084490741</v>
       </c>
       <c r="F18" s="19" t="n">
@@ -8078,10 +8083,10 @@
       <c r="C19" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="36" t="n">
         <v>46273.02431712963</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="36" t="n">
         <v>46273.96641203704</v>
       </c>
       <c r="F19" s="20" t="n">
@@ -8133,10 +8138,10 @@
       <c r="C20" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="35" t="n">
         <v>46274.0233912037</v>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E20" s="35" t="n">
         <v>46274.92560185185</v>
       </c>
       <c r="F20" s="19" t="n">
@@ -8188,10 +8193,10 @@
       <c r="C21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="36" t="n">
         <v>46275.02995370371</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E21" s="36" t="n">
         <v>46275.94020833333</v>
       </c>
       <c r="F21" s="20" t="n">
@@ -8243,10 +8248,10 @@
       <c r="C22" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="35" t="n">
         <v>46276.02586805556</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="35" t="n">
         <v>46276.94533564815</v>
       </c>
       <c r="F22" s="19" t="n">
@@ -8298,10 +8303,10 @@
       <c r="C23" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D23" s="40" t="n">
+      <c r="D23" s="36" t="n">
         <v>46277.04614583333</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E23" s="36" t="n">
         <v>46277.98825231481</v>
       </c>
       <c r="F23" s="20" t="n">
@@ -8353,10 +8358,10 @@
       <c r="C24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="35" t="n">
         <v>46278.03136574074</v>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E24" s="35" t="n">
         <v>46278.99358796296</v>
       </c>
       <c r="F24" s="19">
@@ -8409,10 +8414,10 @@
       <c r="C25" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="D25" s="40" t="n">
+      <c r="D25" s="36" t="n">
         <v>46279.01908564815</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E25" s="36" t="n">
         <v>46279.88167824074</v>
       </c>
       <c r="F25" s="20">
@@ -8469,10 +8474,10 @@
       <c r="C26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="35" t="n">
         <v>46280.02366898148</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="35" t="n">
         <v>46280.91341435185</v>
       </c>
       <c r="F26" s="19">
@@ -8525,10 +8530,10 @@
       <c r="C27" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="36" t="n">
         <v>46281.02523148148</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E27" s="36" t="n">
         <v>46281.85599537037</v>
       </c>
       <c r="F27" s="20">
@@ -8581,10 +8586,10 @@
       <c r="C28" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="35" t="n">
         <v>46282.02123842593</v>
       </c>
-      <c r="E28" s="39" t="n">
+      <c r="E28" s="35" t="n">
         <v>46282.86744212963</v>
       </c>
       <c r="F28" s="19">
@@ -8635,24 +8640,50 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="40" t="n"/>
-      <c r="E29" s="40" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:31:00</t>
+        </is>
+      </c>
+      <c r="E29" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:20:32</t>
+        </is>
+      </c>
       <c r="F29" s="20">
         <f>IF(OR(D29="",E29=""),"",24*(E29-D29))</f>
         <v/>
       </c>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="22" t="n"/>
-      <c r="N29" s="22" t="n"/>
+      <c r="G29" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>1562</v>
+      </c>
+      <c r="J29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v>158</v>
+      </c>
+      <c r="L29" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="M29" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" s="22" t="n">
+        <v>14371</v>
+      </c>
       <c r="O29" s="22" t="n">
         <v>5</v>
       </c>
@@ -8661,7 +8692,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q29" s="13" t="n"/>
+      <c r="Q29" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 28; deploy: manual; artifact không lưu; scraper_version=2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
@@ -8673,8 +8708,8 @@
         </is>
       </c>
       <c r="C30" s="12" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="39" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
       <c r="F30" s="19">
         <f>IF(OR(D30="",E30=""),"",24*(E30-D30))</f>
         <v/>
@@ -8707,8 +8742,8 @@
         </is>
       </c>
       <c r="C31" s="13" t="n"/>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="40" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
       <c r="F31" s="20">
         <f>IF(OR(D31="",E31=""),"",24*(E31-D31))</f>
         <v/>
@@ -8741,8 +8776,8 @@
         </is>
       </c>
       <c r="C32" s="12" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="39" t="n"/>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
       <c r="F32" s="19">
         <f>IF(OR(D32="",E32=""),"",24*(E32-D32))</f>
         <v/>
@@ -8775,8 +8810,8 @@
         </is>
       </c>
       <c r="C33" s="13" t="n"/>
-      <c r="D33" s="40" t="n"/>
-      <c r="E33" s="40" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="36" t="n"/>
       <c r="F33" s="20">
         <f>IF(OR(D33="",E33=""),"",24*(E33-D33))</f>
         <v/>
@@ -8809,8 +8844,8 @@
         </is>
       </c>
       <c r="C34" s="12" t="n"/>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="39" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
       <c r="F34" s="19">
         <f>IF(OR(D34="",E34=""),"",24*(E34-D34))</f>
         <v/>
@@ -8843,8 +8878,8 @@
         </is>
       </c>
       <c r="C35" s="13" t="n"/>
-      <c r="D35" s="40" t="n"/>
-      <c r="E35" s="40" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
       <c r="F35" s="20">
         <f>IF(OR(D35="",E35=""),"",24*(E35-D35))</f>
         <v/>
@@ -8877,8 +8912,8 @@
         </is>
       </c>
       <c r="C36" s="12" t="n"/>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="39" t="n"/>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
       <c r="F36" s="19">
         <f>IF(OR(D36="",E36=""),"",24*(E36-D36))</f>
         <v/>
@@ -8911,8 +8946,8 @@
         </is>
       </c>
       <c r="C37" s="13" t="n"/>
-      <c r="D37" s="40" t="n"/>
-      <c r="E37" s="40" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
       <c r="F37" s="20">
         <f>IF(OR(D37="",E37=""),"",24*(E37-D37))</f>
         <v/>
@@ -8945,8 +8980,8 @@
         </is>
       </c>
       <c r="C38" s="12" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="39" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
       <c r="F38" s="19">
         <f>IF(OR(D38="",E38=""),"",24*(E38-D38))</f>
         <v/>
@@ -8979,8 +9014,8 @@
         </is>
       </c>
       <c r="C39" s="13" t="n"/>
-      <c r="D39" s="40" t="n"/>
-      <c r="E39" s="40" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
       <c r="F39" s="20">
         <f>IF(OR(D39="",E39=""),"",24*(E39-D39))</f>
         <v/>
@@ -9013,8 +9048,8 @@
         </is>
       </c>
       <c r="C40" s="12" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="39" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
       <c r="F40" s="19">
         <f>IF(OR(D40="",E40=""),"",24*(E40-D40))</f>
         <v/>
@@ -9047,8 +9082,8 @@
         </is>
       </c>
       <c r="C41" s="13" t="n"/>
-      <c r="D41" s="40" t="n"/>
-      <c r="E41" s="40" t="n"/>
+      <c r="D41" s="36" t="n"/>
+      <c r="E41" s="36" t="n"/>
       <c r="F41" s="20">
         <f>IF(OR(D41="",E41=""),"",24*(E41-D41))</f>
         <v/>
@@ -9081,8 +9116,8 @@
         </is>
       </c>
       <c r="C42" s="12" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="39" t="n"/>
+      <c r="D42" s="35" t="n"/>
+      <c r="E42" s="35" t="n"/>
       <c r="F42" s="19">
         <f>IF(OR(D42="",E42=""),"",24*(E42-D42))</f>
         <v/>
@@ -9115,8 +9150,8 @@
         </is>
       </c>
       <c r="C43" s="13" t="n"/>
-      <c r="D43" s="40" t="n"/>
-      <c r="E43" s="40" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
       <c r="F43" s="20">
         <f>IF(OR(D43="",E43=""),"",24*(E43-D43))</f>
         <v/>
@@ -9149,8 +9184,8 @@
         </is>
       </c>
       <c r="C44" s="12" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="39" t="n"/>
+      <c r="D44" s="35" t="n"/>
+      <c r="E44" s="35" t="n"/>
       <c r="F44" s="19">
         <f>IF(OR(D44="",E44=""),"",24*(E44-D44))</f>
         <v/>
@@ -9183,8 +9218,8 @@
         </is>
       </c>
       <c r="C45" s="13" t="n"/>
-      <c r="D45" s="40" t="n"/>
-      <c r="E45" s="40" t="n"/>
+      <c r="D45" s="36" t="n"/>
+      <c r="E45" s="36" t="n"/>
       <c r="F45" s="20">
         <f>IF(OR(D45="",E45=""),"",24*(E45-D45))</f>
         <v/>
@@ -9217,8 +9252,8 @@
         </is>
       </c>
       <c r="C46" s="12" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="39" t="n"/>
+      <c r="D46" s="35" t="n"/>
+      <c r="E46" s="35" t="n"/>
       <c r="F46" s="19">
         <f>IF(OR(D46="",E46=""),"",24*(E46-D46))</f>
         <v/>
@@ -9251,8 +9286,8 @@
         </is>
       </c>
       <c r="C47" s="13" t="n"/>
-      <c r="D47" s="40" t="n"/>
-      <c r="E47" s="40" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
       <c r="F47" s="20">
         <f>IF(OR(D47="",E47=""),"",24*(E47-D47))</f>
         <v/>
@@ -9285,8 +9320,8 @@
         </is>
       </c>
       <c r="C48" s="12" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="39" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
       <c r="F48" s="19">
         <f>IF(OR(D48="",E48=""),"",24*(E48-D48))</f>
         <v/>
@@ -9319,8 +9354,8 @@
         </is>
       </c>
       <c r="C49" s="13" t="n"/>
-      <c r="D49" s="40" t="n"/>
-      <c r="E49" s="40" t="n"/>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
       <c r="F49" s="20">
         <f>IF(OR(D49="",E49=""),"",24*(E49-D49))</f>
         <v/>
@@ -9353,8 +9388,8 @@
         </is>
       </c>
       <c r="C50" s="12" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="39" t="n"/>
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="35" t="n"/>
       <c r="F50" s="19">
         <f>IF(OR(D50="",E50=""),"",24*(E50-D50))</f>
         <v/>
@@ -9387,8 +9422,8 @@
         </is>
       </c>
       <c r="C51" s="13" t="n"/>
-      <c r="D51" s="40" t="n"/>
-      <c r="E51" s="40" t="n"/>
+      <c r="D51" s="36" t="n"/>
+      <c r="E51" s="36" t="n"/>
       <c r="F51" s="20">
         <f>IF(OR(D51="",E51=""),"",24*(E51-D51))</f>
         <v/>
@@ -9421,8 +9456,8 @@
         </is>
       </c>
       <c r="C52" s="12" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="39" t="n"/>
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="35" t="n"/>
       <c r="F52" s="19">
         <f>IF(OR(D52="",E52=""),"",24*(E52-D52))</f>
         <v/>
@@ -9455,8 +9490,8 @@
         </is>
       </c>
       <c r="C53" s="13" t="n"/>
-      <c r="D53" s="40" t="n"/>
-      <c r="E53" s="40" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
       <c r="F53" s="20">
         <f>IF(OR(D53="",E53=""),"",24*(E53-D53))</f>
         <v/>
@@ -9489,8 +9524,8 @@
         </is>
       </c>
       <c r="C54" s="12" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="39" t="n"/>
+      <c r="D54" s="35" t="n"/>
+      <c r="E54" s="35" t="n"/>
       <c r="F54" s="19">
         <f>IF(OR(D54="",E54=""),"",24*(E54-D54))</f>
         <v/>
@@ -9523,8 +9558,8 @@
         </is>
       </c>
       <c r="C55" s="13" t="n"/>
-      <c r="D55" s="40" t="n"/>
-      <c r="E55" s="40" t="n"/>
+      <c r="D55" s="36" t="n"/>
+      <c r="E55" s="36" t="n"/>
       <c r="F55" s="20">
         <f>IF(OR(D55="",E55=""),"",24*(E55-D55))</f>
         <v/>
@@ -9557,8 +9592,8 @@
         </is>
       </c>
       <c r="C56" s="12" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="39" t="n"/>
+      <c r="D56" s="35" t="n"/>
+      <c r="E56" s="35" t="n"/>
       <c r="F56" s="19">
         <f>IF(OR(D56="",E56=""),"",24*(E56-D56))</f>
         <v/>
@@ -9591,8 +9626,8 @@
         </is>
       </c>
       <c r="C57" s="13" t="n"/>
-      <c r="D57" s="40" t="n"/>
-      <c r="E57" s="40" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
       <c r="F57" s="20">
         <f>IF(OR(D57="",E57=""),"",24*(E57-D57))</f>
         <v/>
@@ -9625,8 +9660,8 @@
         </is>
       </c>
       <c r="C58" s="12" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="39" t="n"/>
+      <c r="D58" s="35" t="n"/>
+      <c r="E58" s="35" t="n"/>
       <c r="F58" s="19">
         <f>IF(OR(D58="",E58=""),"",24*(E58-D58))</f>
         <v/>
@@ -9659,8 +9694,8 @@
         </is>
       </c>
       <c r="C59" s="13" t="n"/>
-      <c r="D59" s="40" t="n"/>
-      <c r="E59" s="40" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
       <c r="F59" s="20">
         <f>IF(OR(D59="",E59=""),"",24*(E59-D59))</f>
         <v/>
@@ -9693,8 +9728,8 @@
         </is>
       </c>
       <c r="C60" s="12" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="39" t="n"/>
+      <c r="D60" s="35" t="n"/>
+      <c r="E60" s="35" t="n"/>
       <c r="F60" s="19">
         <f>IF(OR(D60="",E60=""),"",24*(E60-D60))</f>
         <v/>
@@ -9727,8 +9762,8 @@
         </is>
       </c>
       <c r="C61" s="13" t="n"/>
-      <c r="D61" s="40" t="n"/>
-      <c r="E61" s="40" t="n"/>
+      <c r="D61" s="36" t="n"/>
+      <c r="E61" s="36" t="n"/>
       <c r="F61" s="20">
         <f>IF(OR(D61="",E61=""),"",24*(E61-D61))</f>
         <v/>
@@ -9761,8 +9796,8 @@
         </is>
       </c>
       <c r="C62" s="12" t="n"/>
-      <c r="D62" s="39" t="n"/>
-      <c r="E62" s="39" t="n"/>
+      <c r="D62" s="35" t="n"/>
+      <c r="E62" s="35" t="n"/>
       <c r="F62" s="19">
         <f>IF(OR(D62="",E62=""),"",24*(E62-D62))</f>
         <v/>
@@ -9795,8 +9830,8 @@
         </is>
       </c>
       <c r="C63" s="13" t="n"/>
-      <c r="D63" s="40" t="n"/>
-      <c r="E63" s="40" t="n"/>
+      <c r="D63" s="36" t="n"/>
+      <c r="E63" s="36" t="n"/>
       <c r="F63" s="20">
         <f>IF(OR(D63="",E63=""),"",24*(E63-D63))</f>
         <v/>
@@ -9829,8 +9864,8 @@
         </is>
       </c>
       <c r="C64" s="12" t="n"/>
-      <c r="D64" s="39" t="n"/>
-      <c r="E64" s="39" t="n"/>
+      <c r="D64" s="35" t="n"/>
+      <c r="E64" s="35" t="n"/>
       <c r="F64" s="19">
         <f>IF(OR(D64="",E64=""),"",24*(E64-D64))</f>
         <v/>
@@ -9863,8 +9898,8 @@
         </is>
       </c>
       <c r="C65" s="13" t="n"/>
-      <c r="D65" s="40" t="n"/>
-      <c r="E65" s="40" t="n"/>
+      <c r="D65" s="36" t="n"/>
+      <c r="E65" s="36" t="n"/>
       <c r="F65" s="20">
         <f>IF(OR(D65="",E65=""),"",24*(E65-D65))</f>
         <v/>
@@ -9897,8 +9932,8 @@
         </is>
       </c>
       <c r="C66" s="12" t="n"/>
-      <c r="D66" s="39" t="n"/>
-      <c r="E66" s="39" t="n"/>
+      <c r="D66" s="35" t="n"/>
+      <c r="E66" s="35" t="n"/>
       <c r="F66" s="19">
         <f>IF(OR(D66="",E66=""),"",24*(E66-D66))</f>
         <v/>
@@ -9931,8 +9966,8 @@
         </is>
       </c>
       <c r="C67" s="13" t="n"/>
-      <c r="D67" s="40" t="n"/>
-      <c r="E67" s="40" t="n"/>
+      <c r="D67" s="36" t="n"/>
+      <c r="E67" s="36" t="n"/>
       <c r="F67" s="20">
         <f>IF(OR(D67="",E67=""),"",24*(E67-D67))</f>
         <v/>
@@ -9965,8 +10000,8 @@
         </is>
       </c>
       <c r="C68" s="12" t="n"/>
-      <c r="D68" s="39" t="n"/>
-      <c r="E68" s="39" t="n"/>
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
       <c r="F68" s="19">
         <f>IF(OR(D68="",E68=""),"",24*(E68-D68))</f>
         <v/>
@@ -9999,8 +10034,8 @@
         </is>
       </c>
       <c r="C69" s="13" t="n"/>
-      <c r="D69" s="40" t="n"/>
-      <c r="E69" s="40" t="n"/>
+      <c r="D69" s="36" t="n"/>
+      <c r="E69" s="36" t="n"/>
       <c r="F69" s="20">
         <f>IF(OR(D69="",E69=""),"",24*(E69-D69))</f>
         <v/>
@@ -10033,8 +10068,8 @@
         </is>
       </c>
       <c r="C70" s="12" t="n"/>
-      <c r="D70" s="39" t="n"/>
-      <c r="E70" s="39" t="n"/>
+      <c r="D70" s="35" t="n"/>
+      <c r="E70" s="35" t="n"/>
       <c r="F70" s="19">
         <f>IF(OR(D70="",E70=""),"",24*(E70-D70))</f>
         <v/>
@@ -10067,8 +10102,8 @@
         </is>
       </c>
       <c r="C71" s="13" t="n"/>
-      <c r="D71" s="40" t="n"/>
-      <c r="E71" s="40" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
       <c r="F71" s="20">
         <f>IF(OR(D71="",E71=""),"",24*(E71-D71))</f>
         <v/>
@@ -10101,8 +10136,8 @@
         </is>
       </c>
       <c r="C72" s="12" t="n"/>
-      <c r="D72" s="39" t="n"/>
-      <c r="E72" s="39" t="n"/>
+      <c r="D72" s="35" t="n"/>
+      <c r="E72" s="35" t="n"/>
       <c r="F72" s="19">
         <f>IF(OR(D72="",E72=""),"",24*(E72-D72))</f>
         <v/>
@@ -10135,8 +10170,8 @@
         </is>
       </c>
       <c r="C73" s="13" t="n"/>
-      <c r="D73" s="40" t="n"/>
-      <c r="E73" s="40" t="n"/>
+      <c r="D73" s="36" t="n"/>
+      <c r="E73" s="36" t="n"/>
       <c r="F73" s="20">
         <f>IF(OR(D73="",E73=""),"",24*(E73-D73))</f>
         <v/>
@@ -10169,8 +10204,8 @@
         </is>
       </c>
       <c r="C74" s="12" t="n"/>
-      <c r="D74" s="39" t="n"/>
-      <c r="E74" s="39" t="n"/>
+      <c r="D74" s="35" t="n"/>
+      <c r="E74" s="35" t="n"/>
       <c r="F74" s="19">
         <f>IF(OR(D74="",E74=""),"",24*(E74-D74))</f>
         <v/>
@@ -10203,8 +10238,8 @@
         </is>
       </c>
       <c r="C75" s="13" t="n"/>
-      <c r="D75" s="40" t="n"/>
-      <c r="E75" s="40" t="n"/>
+      <c r="D75" s="36" t="n"/>
+      <c r="E75" s="36" t="n"/>
       <c r="F75" s="20">
         <f>IF(OR(D75="",E75=""),"",24*(E75-D75))</f>
         <v/>
@@ -10237,8 +10272,8 @@
         </is>
       </c>
       <c r="C76" s="12" t="n"/>
-      <c r="D76" s="39" t="n"/>
-      <c r="E76" s="39" t="n"/>
+      <c r="D76" s="35" t="n"/>
+      <c r="E76" s="35" t="n"/>
       <c r="F76" s="19">
         <f>IF(OR(D76="",E76=""),"",24*(E76-D76))</f>
         <v/>
@@ -10271,8 +10306,8 @@
         </is>
       </c>
       <c r="C77" s="13" t="n"/>
-      <c r="D77" s="40" t="n"/>
-      <c r="E77" s="40" t="n"/>
+      <c r="D77" s="36" t="n"/>
+      <c r="E77" s="36" t="n"/>
       <c r="F77" s="20">
         <f>IF(OR(D77="",E77=""),"",24*(E77-D77))</f>
         <v/>
@@ -10305,8 +10340,8 @@
         </is>
       </c>
       <c r="C78" s="12" t="n"/>
-      <c r="D78" s="39" t="n"/>
-      <c r="E78" s="39" t="n"/>
+      <c r="D78" s="35" t="n"/>
+      <c r="E78" s="35" t="n"/>
       <c r="F78" s="19">
         <f>IF(OR(D78="",E78=""),"",24*(E78-D78))</f>
         <v/>
@@ -10339,8 +10374,8 @@
         </is>
       </c>
       <c r="C79" s="13" t="n"/>
-      <c r="D79" s="40" t="n"/>
-      <c r="E79" s="40" t="n"/>
+      <c r="D79" s="36" t="n"/>
+      <c r="E79" s="36" t="n"/>
       <c r="F79" s="20">
         <f>IF(OR(D79="",E79=""),"",24*(E79-D79))</f>
         <v/>
@@ -10373,8 +10408,8 @@
         </is>
       </c>
       <c r="C80" s="12" t="n"/>
-      <c r="D80" s="39" t="n"/>
-      <c r="E80" s="39" t="n"/>
+      <c r="D80" s="35" t="n"/>
+      <c r="E80" s="35" t="n"/>
       <c r="F80" s="19">
         <f>IF(OR(D80="",E80=""),"",24*(E80-D80))</f>
         <v/>
@@ -10407,8 +10442,8 @@
         </is>
       </c>
       <c r="C81" s="13" t="n"/>
-      <c r="D81" s="40" t="n"/>
-      <c r="E81" s="40" t="n"/>
+      <c r="D81" s="36" t="n"/>
+      <c r="E81" s="36" t="n"/>
       <c r="F81" s="20">
         <f>IF(OR(D81="",E81=""),"",24*(E81-D81))</f>
         <v/>
@@ -10441,8 +10476,8 @@
         </is>
       </c>
       <c r="C82" s="12" t="n"/>
-      <c r="D82" s="39" t="n"/>
-      <c r="E82" s="39" t="n"/>
+      <c r="D82" s="35" t="n"/>
+      <c r="E82" s="35" t="n"/>
       <c r="F82" s="19">
         <f>IF(OR(D82="",E82=""),"",24*(E82-D82))</f>
         <v/>
@@ -10475,8 +10510,8 @@
         </is>
       </c>
       <c r="C83" s="13" t="n"/>
-      <c r="D83" s="40" t="n"/>
-      <c r="E83" s="40" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
       <c r="F83" s="20">
         <f>IF(OR(D83="",E83=""),"",24*(E83-D83))</f>
         <v/>
@@ -10509,8 +10544,8 @@
         </is>
       </c>
       <c r="C84" s="12" t="n"/>
-      <c r="D84" s="39" t="n"/>
-      <c r="E84" s="39" t="n"/>
+      <c r="D84" s="35" t="n"/>
+      <c r="E84" s="35" t="n"/>
       <c r="F84" s="19">
         <f>IF(OR(D84="",E84=""),"",24*(E84-D84))</f>
         <v/>
@@ -10543,8 +10578,8 @@
         </is>
       </c>
       <c r="C85" s="13" t="n"/>
-      <c r="D85" s="40" t="n"/>
-      <c r="E85" s="40" t="n"/>
+      <c r="D85" s="36" t="n"/>
+      <c r="E85" s="36" t="n"/>
       <c r="F85" s="20">
         <f>IF(OR(D85="",E85=""),"",24*(E85-D85))</f>
         <v/>
@@ -10577,8 +10612,8 @@
         </is>
       </c>
       <c r="C86" s="12" t="n"/>
-      <c r="D86" s="39" t="n"/>
-      <c r="E86" s="39" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
       <c r="F86" s="19">
         <f>IF(OR(D86="",E86=""),"",24*(E86-D86))</f>
         <v/>
@@ -10611,8 +10646,8 @@
         </is>
       </c>
       <c r="C87" s="13" t="n"/>
-      <c r="D87" s="40" t="n"/>
-      <c r="E87" s="40" t="n"/>
+      <c r="D87" s="36" t="n"/>
+      <c r="E87" s="36" t="n"/>
       <c r="F87" s="20">
         <f>IF(OR(D87="",E87=""),"",24*(E87-D87))</f>
         <v/>
@@ -10645,8 +10680,8 @@
         </is>
       </c>
       <c r="C88" s="12" t="n"/>
-      <c r="D88" s="39" t="n"/>
-      <c r="E88" s="39" t="n"/>
+      <c r="D88" s="35" t="n"/>
+      <c r="E88" s="35" t="n"/>
       <c r="F88" s="19">
         <f>IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
         <v/>
@@ -10679,8 +10714,8 @@
         </is>
       </c>
       <c r="C89" s="13" t="n"/>
-      <c r="D89" s="40" t="n"/>
-      <c r="E89" s="40" t="n"/>
+      <c r="D89" s="36" t="n"/>
+      <c r="E89" s="36" t="n"/>
       <c r="F89" s="20">
         <f>IF(OR(D89="",E89=""),"",24*(E89-D89))</f>
         <v/>
@@ -10713,8 +10748,8 @@
         </is>
       </c>
       <c r="C90" s="12" t="n"/>
-      <c r="D90" s="39" t="n"/>
-      <c r="E90" s="39" t="n"/>
+      <c r="D90" s="35" t="n"/>
+      <c r="E90" s="35" t="n"/>
       <c r="F90" s="19">
         <f>IF(OR(D90="",E90=""),"",24*(E90-D90))</f>
         <v/>
@@ -10747,8 +10782,8 @@
         </is>
       </c>
       <c r="C91" s="13" t="n"/>
-      <c r="D91" s="40" t="n"/>
-      <c r="E91" s="40" t="n"/>
+      <c r="D91" s="36" t="n"/>
+      <c r="E91" s="36" t="n"/>
       <c r="F91" s="20">
         <f>IF(OR(D91="",E91=""),"",24*(E91-D91))</f>
         <v/>
@@ -10781,8 +10816,8 @@
         </is>
       </c>
       <c r="C92" s="12" t="n"/>
-      <c r="D92" s="39" t="n"/>
-      <c r="E92" s="39" t="n"/>
+      <c r="D92" s="35" t="n"/>
+      <c r="E92" s="35" t="n"/>
       <c r="F92" s="19">
         <f>IF(OR(D92="",E92=""),"",24*(E92-D92))</f>
         <v/>
@@ -10815,8 +10850,8 @@
         </is>
       </c>
       <c r="C93" s="13" t="n"/>
-      <c r="D93" s="40" t="n"/>
-      <c r="E93" s="40" t="n"/>
+      <c r="D93" s="36" t="n"/>
+      <c r="E93" s="36" t="n"/>
       <c r="F93" s="20">
         <f>IF(OR(D93="",E93=""),"",24*(E93-D93))</f>
         <v/>
@@ -10849,8 +10884,8 @@
         </is>
       </c>
       <c r="C94" s="12" t="n"/>
-      <c r="D94" s="39" t="n"/>
-      <c r="E94" s="39" t="n"/>
+      <c r="D94" s="35" t="n"/>
+      <c r="E94" s="35" t="n"/>
       <c r="F94" s="19">
         <f>IF(OR(D94="",E94=""),"",24*(E94-D94))</f>
         <v/>
@@ -10883,8 +10918,8 @@
         </is>
       </c>
       <c r="C95" s="13" t="n"/>
-      <c r="D95" s="40" t="n"/>
-      <c r="E95" s="40" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
       <c r="F95" s="20">
         <f>IF(OR(D95="",E95=""),"",24*(E95-D95))</f>
         <v/>
@@ -10917,8 +10952,8 @@
         </is>
       </c>
       <c r="C96" s="12" t="n"/>
-      <c r="D96" s="39" t="n"/>
-      <c r="E96" s="39" t="n"/>
+      <c r="D96" s="35" t="n"/>
+      <c r="E96" s="35" t="n"/>
       <c r="F96" s="19">
         <f>IF(OR(D96="",E96=""),"",24*(E96-D96))</f>
         <v/>
@@ -10951,8 +10986,8 @@
         </is>
       </c>
       <c r="C97" s="13" t="n"/>
-      <c r="D97" s="40" t="n"/>
-      <c r="E97" s="40" t="n"/>
+      <c r="D97" s="36" t="n"/>
+      <c r="E97" s="36" t="n"/>
       <c r="F97" s="20">
         <f>IF(OR(D97="",E97=""),"",24*(E97-D97))</f>
         <v/>
@@ -10985,8 +11020,8 @@
         </is>
       </c>
       <c r="C98" s="12" t="n"/>
-      <c r="D98" s="39" t="n"/>
-      <c r="E98" s="39" t="n"/>
+      <c r="D98" s="35" t="n"/>
+      <c r="E98" s="35" t="n"/>
       <c r="F98" s="19">
         <f>IF(OR(D98="",E98=""),"",24*(E98-D98))</f>
         <v/>
@@ -11019,8 +11054,8 @@
         </is>
       </c>
       <c r="C99" s="13" t="n"/>
-      <c r="D99" s="40" t="n"/>
-      <c r="E99" s="40" t="n"/>
+      <c r="D99" s="36" t="n"/>
+      <c r="E99" s="36" t="n"/>
       <c r="F99" s="20">
         <f>IF(OR(D99="",E99=""),"",24*(E99-D99))</f>
         <v/>
@@ -11053,8 +11088,8 @@
         </is>
       </c>
       <c r="C100" s="12" t="n"/>
-      <c r="D100" s="39" t="n"/>
-      <c r="E100" s="39" t="n"/>
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="35" t="n"/>
       <c r="F100" s="19">
         <f>IF(OR(D100="",E100=""),"",24*(E100-D100))</f>
         <v/>
@@ -11087,8 +11122,8 @@
         </is>
       </c>
       <c r="C101" s="13" t="n"/>
-      <c r="D101" s="40" t="n"/>
-      <c r="E101" s="40" t="n"/>
+      <c r="D101" s="36" t="n"/>
+      <c r="E101" s="36" t="n"/>
       <c r="F101" s="20">
         <f>IF(OR(D101="",E101=""),"",24*(E101-D101))</f>
         <v/>
@@ -11121,8 +11156,8 @@
         </is>
       </c>
       <c r="C102" s="12" t="n"/>
-      <c r="D102" s="39" t="n"/>
-      <c r="E102" s="39" t="n"/>
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="35" t="n"/>
       <c r="F102" s="19">
         <f>IF(OR(D102="",E102=""),"",24*(E102-D102))</f>
         <v/>
@@ -11177,28 +11212,28 @@
   <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="14" customWidth="1" style="36" min="1" max="1"/>
-    <col width="13" customWidth="1" style="36" min="2" max="2"/>
-    <col width="12" customWidth="1" style="36" min="3" max="3"/>
-    <col width="13" customWidth="1" style="36" min="4" max="15"/>
-    <col width="27" customWidth="1" style="36" min="16" max="16"/>
+    <col width="14" customWidth="1" style="40" min="1" max="1"/>
+    <col width="13" customWidth="1" style="40" min="2" max="2"/>
+    <col width="12" customWidth="1" style="40" min="3" max="3"/>
+    <col width="13" customWidth="1" style="40" min="4" max="15"/>
+    <col width="27" customWidth="1" style="40" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>LOCAL REFERENCE — 12 CHECK-IN DÙNG ĐỂ LOẠI TRÙNG</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Nguồn: D:/MSE/CAPSTONE/outputs/crawl-data-planner-20260816/crawl_sampling_master.xlsx. Đây là snapshot lịch local tại thời điểm tạo workbook VPS; cập nhật lại file VPS nếu lịch local thay đổi.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Crawl date</t>
@@ -16845,21 +16880,22 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="20" customWidth="1" style="36" min="1" max="1"/>
-    <col width="25" customWidth="1" style="36" min="2" max="2"/>
-    <col width="44" customWidth="1" style="36" min="3" max="3"/>
-    <col width="66" customWidth="1" style="36" min="4" max="4"/>
-    <col width="38" customWidth="1" style="36" min="5" max="6"/>
+    <col width="20" customWidth="1" style="40" min="1" max="1"/>
+    <col width="25" customWidth="1" style="40" min="2" max="2"/>
+    <col width="44" customWidth="1" style="40" min="3" max="3"/>
+    <col width="66" customWidth="1" style="40" min="4" max="4"/>
+    <col width="38" customWidth="1" style="40" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>QUY TẮC 5 SLOT VPS BỔ SUNG</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Slot</t>
@@ -16891,7 +16927,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1" s="36">
+    <row r="4" ht="38" customHeight="1" s="40">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>V1 weekday</t>
@@ -16923,7 +16959,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="38" customHeight="1" s="36">
+    <row r="5" ht="38" customHeight="1" s="40">
       <c r="A5" s="33" t="inlineStr">
         <is>
           <t>V2 weekend</t>
@@ -16955,7 +16991,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="38" customHeight="1" s="36">
+    <row r="6" ht="38" customHeight="1" s="40">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>V3 seasonal</t>
@@ -16987,7 +17023,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="38" customHeight="1" s="36">
+    <row r="7" ht="38" customHeight="1" s="40">
       <c r="A7" s="33" t="inlineStr">
         <is>
           <t>V4 medium</t>
@@ -17019,7 +17055,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1" s="36">
+    <row r="8" ht="38" customHeight="1" s="40">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>V5 long</t>
@@ -17051,7 +17087,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="38" customHeight="1" s="36">
+    <row r="9" ht="38" customHeight="1" s="40">
       <c r="A9" s="34" t="n"/>
       <c r="B9" s="34" t="n"/>
       <c r="C9" s="34" t="n"/>
@@ -17059,7 +17095,7 @@
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n"/>
     </row>
-    <row r="10" ht="38" customHeight="1" s="36">
+    <row r="10" ht="38" customHeight="1" s="40">
       <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Quy tắc chung</t>
@@ -17079,7 +17115,7 @@
       <c r="E10" s="24" t="n"/>
       <c r="F10" s="25" t="n"/>
     </row>
-    <row r="11" ht="38" customHeight="1" s="36">
+    <row r="11" ht="38" customHeight="1" s="40">
       <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Lead time 0</t>
@@ -17099,7 +17135,7 @@
       <c r="E11" s="27" t="n"/>
       <c r="F11" s="28" t="n"/>
     </row>
-    <row r="12" ht="38" customHeight="1" s="36">
+    <row r="12" ht="38" customHeight="1" s="40">
       <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Thay đổi local</t>
@@ -17139,20 +17175,21 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="10" customWidth="1" style="36" min="1" max="1"/>
-    <col width="48" customWidth="1" style="36" min="2" max="2"/>
-    <col width="42" customWidth="1" style="36" min="3" max="3"/>
-    <col width="44" customWidth="1" style="36" min="4" max="4"/>
+    <col width="10" customWidth="1" style="40" min="1" max="1"/>
+    <col width="48" customWidth="1" style="40" min="2" max="2"/>
+    <col width="42" customWidth="1" style="40" min="3" max="3"/>
+    <col width="44" customWidth="1" style="40" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="36">
-      <c r="A1" s="35" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="40">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN SỬ DỤNG LỊCH CRAWL VPS</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" s="36">
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Bước</t>
@@ -17174,7 +17211,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1" s="36">
+    <row r="4" ht="34" customHeight="1" s="40">
       <c r="A4" s="32" t="n">
         <v>1</v>
       </c>
@@ -17194,7 +17231,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1" s="36">
+    <row r="5" ht="34" customHeight="1" s="40">
       <c r="A5" s="33" t="n">
         <v>2</v>
       </c>
@@ -17214,7 +17251,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1" s="36">
+    <row r="6" ht="34" customHeight="1" s="40">
       <c r="A6" s="32" t="n">
         <v>3</v>
       </c>
@@ -17234,7 +17271,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1" s="36">
+    <row r="7" ht="34" customHeight="1" s="40">
       <c r="A7" s="33" t="n">
         <v>4</v>
       </c>
@@ -17254,7 +17291,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1" s="36">
+    <row r="8" ht="34" customHeight="1" s="40">
       <c r="A8" s="32" t="n">
         <v>5</v>
       </c>
@@ -17274,7 +17311,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1" s="36">
+    <row r="9" ht="34" customHeight="1" s="40">
       <c r="A9" s="33" t="n">
         <v>6</v>
       </c>
@@ -17294,7 +17331,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" s="36">
+    <row r="10" ht="34" customHeight="1" s="40">
       <c r="A10" s="32" t="n">
         <v>7</v>
       </c>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\CAPSTONE\outputs\vps-crawl-planner-20260823\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4DE907-DA20-44FE-80E1-1D63B5A28EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA24D08-9D77-4368-A686-DD41C0745B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="158">
   <si>
     <t>LỊCH CRAWL VPS BỔ SUNG — 24/08/2026 ĐẾN 30/11/2026</t>
   </si>
@@ -504,6 +504,12 @@
   </si>
   <si>
     <t>Đang chạy</t>
+  </si>
+  <si>
+    <t>Thất bại</t>
+  </si>
+  <si>
+    <t>ngày trước đó chạy lâu quá nên lố giờ qua hôm nay</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1395,7 @@
       </c>
       <c r="B13" s="11">
         <f>COUNTIF(CRAWL_LOG!$B$4:$B$102,"Chưa chạy")</f>
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2971,7 +2977,7 @@
       </c>
       <c r="N31" s="13" t="str">
         <f>CRAWL_LOG!B31</f>
-        <v>Chưa chạy</v>
+        <v>Thất bại</v>
       </c>
       <c r="O31" s="13" t="s">
         <v>42</v>
@@ -6542,7 +6548,7 @@
         <v>46411</v>
       </c>
       <c r="J100" s="17">
-        <f t="shared" ref="J100:J131" si="9">MIN(E100:I100)-A100</f>
+        <f t="shared" ref="J100:J102" si="9">MIN(E100:I100)-A100</f>
         <v>11</v>
       </c>
       <c r="K100" s="17">
@@ -8187,7 +8193,7 @@
         <v>46285</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="36"/>
@@ -8210,7 +8216,9 @@
       <c r="P31" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="Q31" s="13"/>
+      <c r="Q31" s="13" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="14">
@@ -9903,7 +9911,7 @@
       <c r="D88" s="35"/>
       <c r="E88" s="35"/>
       <c r="F88" s="19" t="str">
-        <f t="shared" ref="F88:F119" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
+        <f t="shared" ref="F88:F102" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
         <v/>
       </c>
       <c r="G88" s="21"/>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\CAPSTONE\outputs\vps-crawl-planner-20260823\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA24D08-9D77-4368-A686-DD41C0745B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0024610-E416-479A-94C0-F29EAB4B7952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="159">
   <si>
     <t>LỊCH CRAWL VPS BỔ SUNG — 24/08/2026 ĐẾN 30/11/2026</t>
   </si>
@@ -278,6 +278,15 @@
     <t>Run ID 28; deploy: manual; artifact không lưu; scraper_version=2.3.0</t>
   </si>
   <si>
+    <t>2026-09-19 00:30:55</t>
+  </si>
+  <si>
+    <t>2026-09-20 20:23:53</t>
+  </si>
+  <si>
+    <t>Thất bại</t>
+  </si>
+  <si>
     <t>LOCAL REFERENCE — 12 CHECK-IN DÙNG ĐỂ LOẠI TRÙNG</t>
   </si>
   <si>
@@ -503,13 +512,7 @@
     <t>Không sửa LOCAL_REFERENCE bằng tay</t>
   </si>
   <si>
-    <t>Đang chạy</t>
-  </si>
-  <si>
-    <t>Thất bại</t>
-  </si>
-  <si>
-    <t>ngày trước đó chạy lâu quá nên lố giờ qua hôm nay</t>
+    <t>thực tế là do bị lỗi proxy nên kéo dài tới tận hôm sau để chạy lại</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1389,7 @@
       </c>
       <c r="B12" s="10">
         <f>COUNTIF(CRAWL_LOG!$B$4:$B$102,"Hoàn thành")+COUNTIF(CRAWL_LOG!$B$4:$B$102,"Hoàn thành có lỗi")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2925,7 +2928,7 @@
       </c>
       <c r="N30" s="12" t="str">
         <f>CRAWL_LOG!B30</f>
-        <v>Đang chạy</v>
+        <v>Hoàn thành có lỗi</v>
       </c>
       <c r="O30" s="12" t="s">
         <v>42</v>
@@ -6548,7 +6551,7 @@
         <v>46411</v>
       </c>
       <c r="J100" s="17">
-        <f t="shared" ref="J100:J102" si="9">MIN(E100:I100)-A100</f>
+        <f t="shared" ref="J100:J131" si="9">MIN(E100:I100)-A100</f>
         <v>11</v>
       </c>
       <c r="K100" s="17">
@@ -8161,39 +8164,61 @@
         <v>46284</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="C30" s="12">
         <v>29</v>
       </c>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="19" t="str">
+      <c r="D30" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="19">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+        <v>43.882777777849697</v>
+      </c>
+      <c r="G30" s="21">
+        <v>1770</v>
+      </c>
+      <c r="H30" s="21">
+        <v>1770</v>
+      </c>
+      <c r="I30" s="21">
+        <v>1573</v>
+      </c>
+      <c r="J30" s="21">
+        <v>0</v>
+      </c>
+      <c r="K30" s="21">
+        <v>167</v>
+      </c>
+      <c r="L30" s="21">
+        <v>20</v>
+      </c>
+      <c r="M30" s="21">
+        <v>10</v>
+      </c>
+      <c r="N30" s="21">
+        <v>14607</v>
+      </c>
       <c r="O30" s="21">
         <v>5</v>
       </c>
       <c r="P30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="Q30" s="12"/>
+      <c r="Q30" s="12" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="15">
         <v>46285</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="36"/>
@@ -8216,9 +8241,7 @@
       <c r="P31" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="Q31" s="13" t="s">
-        <v>157</v>
-      </c>
+      <c r="Q31" s="13"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="14">
@@ -9911,7 +9934,7 @@
       <c r="D88" s="35"/>
       <c r="E88" s="35"/>
       <c r="F88" s="19" t="str">
-        <f t="shared" ref="F88:F102" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
+        <f t="shared" ref="F88:F119" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
         <v/>
       </c>
       <c r="G88" s="21"/>
@@ -10387,7 +10410,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -10407,7 +10430,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="42" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -10433,46 +10456,46 @@
         <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -10522,7 +10545,7 @@
         <v>46388</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -10572,7 +10595,7 @@
         <v>46388</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -10622,7 +10645,7 @@
         <v>46388</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -10672,7 +10695,7 @@
         <v>46388</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -10722,7 +10745,7 @@
         <v>46388</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -10772,7 +10795,7 @@
         <v>46388</v>
       </c>
       <c r="P9" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -10822,7 +10845,7 @@
         <v>46388</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -10872,7 +10895,7 @@
         <v>46388</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -10922,7 +10945,7 @@
         <v>46388</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -10972,7 +10995,7 @@
         <v>46388</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -11022,7 +11045,7 @@
         <v>46388</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -11072,7 +11095,7 @@
         <v>46388</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -11122,7 +11145,7 @@
         <v>46388</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -11172,7 +11195,7 @@
         <v>46388</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -11222,7 +11245,7 @@
         <v>46388</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -11272,7 +11295,7 @@
         <v>46388</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -11322,7 +11345,7 @@
         <v>46388</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -11372,7 +11395,7 @@
         <v>46388</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -11422,7 +11445,7 @@
         <v>46388</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -11472,7 +11495,7 @@
         <v>46388</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -11522,7 +11545,7 @@
         <v>46388</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -11572,7 +11595,7 @@
         <v>46388</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -11622,7 +11645,7 @@
         <v>46388</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -11672,7 +11695,7 @@
         <v>46388</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -11722,7 +11745,7 @@
         <v>46388</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -11772,7 +11795,7 @@
         <v>46388</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -11822,7 +11845,7 @@
         <v>46388</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -11872,7 +11895,7 @@
         <v>46388</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -11922,7 +11945,7 @@
         <v>46388</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -11972,7 +11995,7 @@
         <v>46388</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -12022,7 +12045,7 @@
         <v>46388</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -12072,7 +12095,7 @@
         <v>46388</v>
       </c>
       <c r="P35" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -12122,7 +12145,7 @@
         <v>46388</v>
       </c>
       <c r="P36" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -12172,7 +12195,7 @@
         <v>46388</v>
       </c>
       <c r="P37" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -12222,7 +12245,7 @@
         <v>46388</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -12272,7 +12295,7 @@
         <v>46388</v>
       </c>
       <c r="P39" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -12322,7 +12345,7 @@
         <v>46388</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -12372,7 +12395,7 @@
         <v>46388</v>
       </c>
       <c r="P41" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -12422,7 +12445,7 @@
         <v>46388</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -12472,7 +12495,7 @@
         <v>46388</v>
       </c>
       <c r="P43" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -12522,7 +12545,7 @@
         <v>46388</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -12572,7 +12595,7 @@
         <v>46388</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -12622,7 +12645,7 @@
         <v>46388</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -12672,7 +12695,7 @@
         <v>46388</v>
       </c>
       <c r="P47" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -12722,7 +12745,7 @@
         <v>46388</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -12772,7 +12795,7 @@
         <v>46388</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -12822,7 +12845,7 @@
         <v>46388</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -12872,7 +12895,7 @@
         <v>46388</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -12922,7 +12945,7 @@
         <v>46388</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -12972,7 +12995,7 @@
         <v>46388</v>
       </c>
       <c r="P53" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -13022,7 +13045,7 @@
         <v>46388</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -13072,7 +13095,7 @@
         <v>46388</v>
       </c>
       <c r="P55" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -13122,7 +13145,7 @@
         <v>46388</v>
       </c>
       <c r="P56" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -13172,7 +13195,7 @@
         <v>46388</v>
       </c>
       <c r="P57" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -13222,7 +13245,7 @@
         <v>46388</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -13272,7 +13295,7 @@
         <v>46388</v>
       </c>
       <c r="P59" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -13322,7 +13345,7 @@
         <v>46388</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -13372,7 +13395,7 @@
         <v>46388</v>
       </c>
       <c r="P61" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -13422,7 +13445,7 @@
         <v>46388</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -13472,7 +13495,7 @@
         <v>46388</v>
       </c>
       <c r="P63" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -13522,7 +13545,7 @@
         <v>46388</v>
       </c>
       <c r="P64" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -13572,7 +13595,7 @@
         <v>46388</v>
       </c>
       <c r="P65" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -13622,7 +13645,7 @@
         <v>46388</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -13672,7 +13695,7 @@
         <v>46388</v>
       </c>
       <c r="P67" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -13722,7 +13745,7 @@
         <v>46388</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -13772,7 +13795,7 @@
         <v>46388</v>
       </c>
       <c r="P69" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -13822,7 +13845,7 @@
         <v>46388</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -13872,7 +13895,7 @@
         <v>46388</v>
       </c>
       <c r="P71" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -13922,7 +13945,7 @@
         <v>46388</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -13972,7 +13995,7 @@
         <v>46388</v>
       </c>
       <c r="P73" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -14022,7 +14045,7 @@
         <v>46388</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -14072,7 +14095,7 @@
         <v>46388</v>
       </c>
       <c r="P75" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -14122,7 +14145,7 @@
         <v>46388</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -14172,7 +14195,7 @@
         <v>46388</v>
       </c>
       <c r="P77" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -14222,7 +14245,7 @@
         <v>46388</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -14272,7 +14295,7 @@
         <v>46388</v>
       </c>
       <c r="P79" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -14322,7 +14345,7 @@
         <v>46388</v>
       </c>
       <c r="P80" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -14372,7 +14395,7 @@
         <v>46388</v>
       </c>
       <c r="P81" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -14422,7 +14445,7 @@
         <v>46388</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -14472,7 +14495,7 @@
         <v>46388</v>
       </c>
       <c r="P83" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -14522,7 +14545,7 @@
         <v>46388</v>
       </c>
       <c r="P84" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -14572,7 +14595,7 @@
         <v>46388</v>
       </c>
       <c r="P85" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -14622,7 +14645,7 @@
         <v>46388</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -14672,7 +14695,7 @@
         <v>46388</v>
       </c>
       <c r="P87" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -14722,7 +14745,7 @@
         <v>46388</v>
       </c>
       <c r="P88" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -14772,7 +14795,7 @@
         <v>46388</v>
       </c>
       <c r="P89" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -14822,7 +14845,7 @@
         <v>46388</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -14872,7 +14895,7 @@
         <v>46388</v>
       </c>
       <c r="P91" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -14922,7 +14945,7 @@
         <v>46388</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -14972,7 +14995,7 @@
         <v>46388</v>
       </c>
       <c r="P93" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -15022,7 +15045,7 @@
         <v>46388</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -15072,7 +15095,7 @@
         <v>46388</v>
       </c>
       <c r="P95" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -15122,7 +15145,7 @@
         <v>46388</v>
       </c>
       <c r="P96" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -15172,7 +15195,7 @@
         <v>46388</v>
       </c>
       <c r="P97" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -15222,7 +15245,7 @@
         <v>46388</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -15272,7 +15295,7 @@
         <v>46388</v>
       </c>
       <c r="P99" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -15322,7 +15345,7 @@
         <v>46388</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -15372,7 +15395,7 @@
         <v>46388</v>
       </c>
       <c r="P101" s="13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -15422,7 +15445,7 @@
         <v>46388</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -15451,7 +15474,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -15461,22 +15484,22 @@
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38" customHeight="1">
@@ -15484,19 +15507,19 @@
         <v>29</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38" customHeight="1">
@@ -15504,19 +15527,19 @@
         <v>30</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="F5" s="33" t="s">
         <v>111</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38" customHeight="1">
@@ -15524,19 +15547,19 @@
         <v>31</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38" customHeight="1">
@@ -15544,19 +15567,19 @@
         <v>32</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38" customHeight="1">
@@ -15564,19 +15587,19 @@
         <v>33</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38" customHeight="1">
@@ -15589,13 +15612,13 @@
     </row>
     <row r="10" spans="1:6" ht="38" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
@@ -15603,13 +15626,13 @@
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1">
       <c r="A11" s="26" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="27"/>
@@ -15617,13 +15640,13 @@
     </row>
     <row r="12" spans="1:6" ht="38" customHeight="1">
       <c r="A12" s="29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
@@ -15653,7 +15676,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B1" s="40"/>
       <c r="C1" s="40"/>
@@ -15661,16 +15684,16 @@
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="34" customHeight="1">
@@ -15678,13 +15701,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
@@ -15692,13 +15715,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
@@ -15706,13 +15729,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
@@ -15720,13 +15743,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
@@ -15734,13 +15757,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
@@ -15748,13 +15771,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" customHeight="1">
@@ -15762,13 +15785,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -8862,24 +8862,46 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="D33" s="36" t="n">
+        <v>46287.02165509259</v>
+      </c>
+      <c r="E33" s="36" t="n">
+        <v>46287.70703703703</v>
+      </c>
       <c r="F33" s="20">
         <f>IF(OR(D33="",E33=""),"",24*(E33-D33))</f>
         <v/>
       </c>
-      <c r="G33" s="22" t="n"/>
-      <c r="H33" s="22" t="n"/>
-      <c r="I33" s="22" t="n"/>
-      <c r="J33" s="22" t="n"/>
-      <c r="K33" s="22" t="n"/>
-      <c r="L33" s="22" t="n"/>
-      <c r="M33" s="22" t="n"/>
-      <c r="N33" s="22" t="n"/>
+      <c r="G33" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>1555</v>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="L33" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="M33" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" s="22" t="n">
+        <v>13934</v>
+      </c>
       <c r="O33" s="22" t="n">
         <v>5</v>
       </c>
@@ -8888,7 +8910,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q33" s="13" t="n"/>
+      <c r="Q33" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 32; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -8922,24 +8922,46 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="35" t="n"/>
-      <c r="E34" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" s="35" t="n">
+        <v>46288.02347222222</v>
+      </c>
+      <c r="E34" s="35" t="n">
+        <v>46288.71672453704</v>
+      </c>
       <c r="F34" s="19">
         <f>IF(OR(D34="",E34=""),"",24*(E34-D34))</f>
         <v/>
       </c>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
+      <c r="G34" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>1558</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>187</v>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>13802</v>
+      </c>
       <c r="O34" s="21" t="n">
         <v>5</v>
       </c>
@@ -8948,7 +8970,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q34" s="12" t="n"/>
+      <c r="Q34" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 33; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -833,7 +833,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1007,7 +1006,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="41" t="inlineStr">
         <is>
@@ -9042,24 +9040,46 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" s="35" t="n">
+        <v>46290.02737268519</v>
+      </c>
+      <c r="E36" s="35" t="n">
+        <v>46290.66277777778</v>
+      </c>
       <c r="F36" s="19">
         <f>IF(OR(D36="",E36=""),"",24*(E36-D36))</f>
         <v/>
       </c>
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
+      <c r="G36" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>1527</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="21" t="n">
+        <v>213</v>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>13661</v>
+      </c>
       <c r="O36" s="21" t="n">
         <v>5</v>
       </c>
@@ -9068,7 +9088,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q36" s="12" t="n"/>
+      <c r="Q36" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 35; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
@@ -17028,7 +17052,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -17322,7 +17345,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -833,6 +833,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1006,6 +1007,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="41" t="inlineStr">
         <is>
@@ -9100,24 +9102,46 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D37" s="36" t="n">
+        <v>46291.02608796296</v>
+      </c>
+      <c r="E37" s="36" t="n">
+        <v>46291.67150462963</v>
+      </c>
       <c r="F37" s="20">
         <f>IF(OR(D37="",E37=""),"",24*(E37-D37))</f>
         <v/>
       </c>
-      <c r="G37" s="22" t="n"/>
-      <c r="H37" s="22" t="n"/>
-      <c r="I37" s="22" t="n"/>
-      <c r="J37" s="22" t="n"/>
-      <c r="K37" s="22" t="n"/>
-      <c r="L37" s="22" t="n"/>
-      <c r="M37" s="22" t="n"/>
-      <c r="N37" s="22" t="n"/>
+      <c r="G37" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H37" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>1526</v>
+      </c>
+      <c r="J37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="L37" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="22" t="n">
+        <v>13951</v>
+      </c>
       <c r="O37" s="22" t="n">
         <v>5</v>
       </c>
@@ -9126,7 +9150,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q37" s="13" t="n"/>
+      <c r="Q37" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 36; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
@@ -17052,6 +17080,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -17345,6 +17374,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="40">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -9162,24 +9162,50 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:33:05</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>2026-09-27 16:20:08</t>
+        </is>
+      </c>
       <c r="F38" s="19">
         <f>IF(OR(D38="",E38=""),"",24*(E38-D38))</f>
         <v/>
       </c>
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
+      <c r="G38" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>1519</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="21" t="n">
+        <v>191</v>
+      </c>
+      <c r="L38" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>13247</v>
+      </c>
       <c r="O38" s="21" t="n">
         <v>5</v>
       </c>
@@ -9188,7 +9214,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q38" s="12" t="n"/>
+      <c r="Q38" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 37; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -9226,24 +9226,46 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D39" s="36" t="n">
+        <v>46292.74356481482</v>
+      </c>
+      <c r="E39" s="36" t="n">
+        <v>46293.41200231481</v>
+      </c>
       <c r="F39" s="20">
         <f>IF(OR(D39="",E39=""),"",24*(E39-D39))</f>
         <v/>
       </c>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="22" t="n"/>
-      <c r="J39" s="22" t="n"/>
-      <c r="K39" s="22" t="n"/>
-      <c r="L39" s="22" t="n"/>
-      <c r="M39" s="22" t="n"/>
-      <c r="N39" s="22" t="n"/>
+      <c r="G39" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>1506</v>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>204</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="M39" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="N39" s="22" t="n">
+        <v>13998</v>
+      </c>
       <c r="O39" s="22" t="n">
         <v>5</v>
       </c>
@@ -9252,7 +9274,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q39" s="13" t="n"/>
+      <c r="Q39" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 38, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -9286,24 +9286,46 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="D40" s="35" t="n">
+        <v>46294.02</v>
+      </c>
+      <c r="E40" s="35" t="n">
+        <v>46294.67763888889</v>
+      </c>
       <c r="F40" s="19">
         <f>IF(OR(D40="",E40=""),"",24*(E40-D40))</f>
         <v/>
       </c>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
+      <c r="G40" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>1511</v>
+      </c>
+      <c r="J40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="21" t="n">
+        <v>204</v>
+      </c>
+      <c r="L40" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="M40" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N40" s="21" t="n">
+        <v>14467</v>
+      </c>
       <c r="O40" s="21" t="n">
         <v>5</v>
       </c>
@@ -9312,7 +9334,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q40" s="12" t="n"/>
+      <c r="Q40" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 39, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -9346,24 +9346,46 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="36" t="n"/>
-      <c r="E41" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D41" s="36" t="n">
+        <v>46295.02291666667</v>
+      </c>
+      <c r="E41" s="36" t="n">
+        <v>46295.63810185185</v>
+      </c>
       <c r="F41" s="20">
         <f>IF(OR(D41="",E41=""),"",24*(E41-D41))</f>
         <v/>
       </c>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="22" t="n"/>
-      <c r="J41" s="22" t="n"/>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="22" t="n"/>
-      <c r="M41" s="22" t="n"/>
-      <c r="N41" s="22" t="n"/>
+      <c r="G41" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H41" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>1510</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>205</v>
+      </c>
+      <c r="L41" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="M41" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="N41" s="22" t="n">
+        <v>14388</v>
+      </c>
       <c r="O41" s="22" t="n">
         <v>5</v>
       </c>
@@ -9372,7 +9394,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q41" s="13" t="n"/>
+      <c r="Q41" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 40, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
@@ -9406,24 +9406,46 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>46296.02202546296</v>
+      </c>
+      <c r="E42" s="35" t="n">
+        <v>46296.67315972222</v>
+      </c>
       <c r="F42" s="19">
         <f>IF(OR(D42="",E42=""),"",24*(E42-D42))</f>
         <v/>
       </c>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21" t="n"/>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="21" t="n"/>
+      <c r="G42" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="21" t="n">
+        <v>206</v>
+      </c>
+      <c r="L42" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="M42" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="N42" s="21" t="n">
+        <v>14286</v>
+      </c>
       <c r="O42" s="21" t="n">
         <v>5</v>
       </c>
@@ -9432,7 +9454,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q42" s="12" t="n"/>
+      <c r="Q42" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 41, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -9706,24 +9706,46 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="D47" s="36" t="n">
+        <v>46301.02130787037</v>
+      </c>
+      <c r="E47" s="36" t="n">
+        <v>46301.67511574074</v>
+      </c>
       <c r="F47" s="20">
         <f>IF(OR(D47="",E47=""),"",24*(E47-D47))</f>
         <v/>
       </c>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="22" t="n"/>
-      <c r="I47" s="22" t="n"/>
-      <c r="J47" s="22" t="n"/>
-      <c r="K47" s="22" t="n"/>
-      <c r="L47" s="22" t="n"/>
-      <c r="M47" s="22" t="n"/>
-      <c r="N47" s="22" t="n"/>
+      <c r="G47" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H47" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>1513</v>
+      </c>
+      <c r="J47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="22" t="n">
+        <v>182</v>
+      </c>
+      <c r="L47" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="M47" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="N47" s="22" t="n">
+        <v>14929</v>
+      </c>
       <c r="O47" s="22" t="n">
         <v>5</v>
       </c>
@@ -9732,7 +9754,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q47" s="13" t="n"/>
+      <c r="Q47" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 46, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -9766,24 +9766,46 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="D48" s="35" t="n">
+        <v>46302.00695601852</v>
+      </c>
+      <c r="E48" s="35" t="n">
+        <v>46302.67622685185</v>
+      </c>
       <c r="F48" s="19">
         <f>IF(OR(D48="",E48=""),"",24*(E48-D48))</f>
         <v/>
       </c>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
+      <c r="G48" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>1519</v>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="21" t="n">
+        <v>176</v>
+      </c>
+      <c r="L48" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="M48" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>14913</v>
+      </c>
       <c r="O48" s="21" t="n">
         <v>5</v>
       </c>
@@ -9792,7 +9814,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q48" s="12" t="n"/>
+      <c r="Q48" s="12" t="inlineStr">
+        <is>
+          <t>Run ID 47, deploy VPS, artifact không lưu, scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -9826,24 +9826,46 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>Chưa chạy</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
+          <t>Hoàn thành có lỗi</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="D49" s="36" t="n">
+        <v>46303.02209490741</v>
+      </c>
+      <c r="E49" s="36" t="n">
+        <v>46303.71767361111</v>
+      </c>
       <c r="F49" s="20">
         <f>IF(OR(D49="",E49=""),"",24*(E49-D49))</f>
         <v/>
       </c>
-      <c r="G49" s="22" t="n"/>
-      <c r="H49" s="22" t="n"/>
-      <c r="I49" s="22" t="n"/>
-      <c r="J49" s="22" t="n"/>
-      <c r="K49" s="22" t="n"/>
-      <c r="L49" s="22" t="n"/>
-      <c r="M49" s="22" t="n"/>
-      <c r="N49" s="22" t="n"/>
+      <c r="G49" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H49" s="22" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>1503</v>
+      </c>
+      <c r="J49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="22" t="n">
+        <v>182</v>
+      </c>
+      <c r="L49" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="M49" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="N49" s="22" t="n">
+        <v>14523</v>
+      </c>
       <c r="O49" s="22" t="n">
         <v>5</v>
       </c>
@@ -9852,7 +9874,11 @@
           <t>vps</t>
         </is>
       </c>
-      <c r="Q49" s="13" t="n"/>
+      <c r="Q49" s="13" t="inlineStr">
+        <is>
+          <t>Run ID 48; deploy VPS; artifact không lưu; scraper_version 2.3.0</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">

--- a/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
+++ b/outputs/vps-crawl-planner-20260823/vps_crawl_sampling_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\CAPSTONE\outputs\vps-crawl-planner-20260823\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7F467-959B-4B72-9D30-9653F179EF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3637353-17D7-44D3-ADFB-10C29947DD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6611,7 +6611,7 @@
         <v>46411</v>
       </c>
       <c r="J100" s="17">
-        <f t="shared" ref="J100:J131" si="9">MIN(E100:I100)-A100</f>
+        <f t="shared" ref="J100:J102" si="9">MIN(E100:I100)-A100</f>
         <v>11</v>
       </c>
       <c r="K100" s="17">
@@ -10426,7 +10426,7 @@
       <c r="D88" s="35"/>
       <c r="E88" s="35"/>
       <c r="F88" s="19" t="str">
-        <f t="shared" ref="F88:F119" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
+        <f t="shared" ref="F88:F102" si="2">IF(OR(D88="",E88=""),"",24*(E88-D88))</f>
         <v/>
       </c>
       <c r="G88" s="21"/>
